--- a/math/02分数.xlsx
+++ b/math/02分数.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484AF361-E5B8-6740-B520-1F60E01B9A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5581F8C-EBF9-4A43-8479-7FA64141CC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{7646BB93-77BC-8146-87CE-21DD51317936}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>1、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -93,10 +93,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>先按照分子分母的最大公因数进行约分，分子分母同时除以 4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>然后再化成带分数 5 和 2 没有最大公因数了</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -117,18 +113,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>约分一定要约分到最简</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通分：将两个异分母的两个分数化成同分母</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最小公倍数：两个或多个数共同的倍数中，最小的那个</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>最大公因数：两个或多个数共有的因数中，最大的那个</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -161,10 +145,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>倍数就是一个数乘以整数得到的结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>加减法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -181,10 +161,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>然后将分母分子同时乘对应的数 得到同分母</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>乘法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -237,10 +213,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>分数转白分数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>先化小数，再乘100%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -254,6 +226,57 @@
   </si>
   <si>
     <t>x/2 + x/3 = 3x+2x/6 = 5x/6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果a能够被b整除，那么b就是a的因数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>约分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分子分母同时除以最大公因数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将两个异分母的两个分数化成同分母</t>
+  </si>
+  <si>
+    <t>因为 2 和 5 互质</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最小公倍数：两个或多个数共有的倍数中，最小的那个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>倍数是指一个数乘以整数得到的结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a*1 a*2 a*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b*1 b*2 b*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例如 2 和 5 的最小公倍数是 10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>然后将分母分子同时乘对应的数，得到同分母</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分数转百分数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -659,13 +682,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89357A94-6808-2749-BC1B-ABA8A280DF54}">
-  <dimension ref="B3:J44"/>
+  <dimension ref="B3:J48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -673,12 +696,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
@@ -689,7 +712,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="D8" s="1" t="s">
         <v>5</v>
       </c>
@@ -697,196 +720,220 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="D9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.15">
       <c r="C12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.15">
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="E15" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="E15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="I15" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>21</v>
+        <v>52</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="I17" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C20" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="J21" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C22" s="1" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C23" s="1" t="s">
-        <v>23</v>
+        <v>51</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C24" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="C25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="C28" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="D29" s="1" t="s">
-        <v>33</v>
+      <c r="I26" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="I27" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="D30" s="1" t="s">
-        <v>34</v>
+      <c r="B30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C32" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="3:8" x14ac:dyDescent="0.15">
       <c r="D33" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="3:8" x14ac:dyDescent="0.15">
-      <c r="C35" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>41</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="D34" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C36" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="D36" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="3:8" x14ac:dyDescent="0.15">
-      <c r="C38" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="D37" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="3:8" x14ac:dyDescent="0.15">
       <c r="D40" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="3:8" x14ac:dyDescent="0.15">
-      <c r="D41" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="3:8" x14ac:dyDescent="0.15">
-      <c r="D42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>51</v>
+      <c r="C42" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="3:8" x14ac:dyDescent="0.15">
       <c r="D44" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="D45" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="D46" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="D48" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/math/02分数.xlsx
+++ b/math/02分数.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5581F8C-EBF9-4A43-8479-7FA64141CC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD1C32F-85A0-6146-A884-1A80F65B09CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{7646BB93-77BC-8146-87CE-21DD51317936}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>1、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -173,10 +173,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>a又c/b = a*b+c/b</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>除法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -277,6 +273,18 @@
   </si>
   <si>
     <t>分数转百分数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GCD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a又c/b = ab+c/b</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -682,13 +690,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89357A94-6808-2749-BC1B-ABA8A280DF54}">
-  <dimension ref="B3:J48"/>
+  <dimension ref="B3:M48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -696,12 +704,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
@@ -712,7 +720,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="D8" s="1" t="s">
         <v>5</v>
       </c>
@@ -720,17 +728,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="D9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C12" s="1" t="s">
         <v>9</v>
       </c>
@@ -738,7 +746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
@@ -746,41 +754,44 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="E14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.15">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="E15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="M15" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="E16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.15">
       <c r="I17" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C18" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C19" s="1" t="s">
         <v>16</v>
       </c>
@@ -788,7 +799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C20" s="1" t="s">
         <v>17</v>
       </c>
@@ -796,49 +807,55 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C22" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C23" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.15">
+        <v>52</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="C25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="C25" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="1" t="s">
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="I26" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="I26" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="I27" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>23</v>
       </c>
@@ -846,7 +863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
@@ -877,63 +894,63 @@
         <v>32</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="3:8" x14ac:dyDescent="0.15">
       <c r="C39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="40" spans="3:8" x14ac:dyDescent="0.15">
       <c r="D40" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="3:8" x14ac:dyDescent="0.15">
       <c r="C42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="3:8" x14ac:dyDescent="0.15">
       <c r="D44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="45" spans="3:8" x14ac:dyDescent="0.15">
       <c r="D45" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="H45" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="46" spans="3:8" x14ac:dyDescent="0.15">
       <c r="D46" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E46" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="48" spans="3:8" x14ac:dyDescent="0.15">
       <c r="D48" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
